--- a/test-data/exceldownloadTest.xlsx
+++ b/test-data/exceldownloadTest.xlsx
@@ -40,7 +40,7 @@
     <t>Summer</t>
   </si>
   <si>
-    <t>Sapota u57vb2</t>
+    <t>Sapota nlr696</t>
   </si>
   <si>
     <t>Red</t>

--- a/test-data/exceldownloadTest.xlsx
+++ b/test-data/exceldownloadTest.xlsx
@@ -40,7 +40,7 @@
     <t>Summer</t>
   </si>
   <si>
-    <t>Sapota nlr696</t>
+    <t>Sapota jvvg14</t>
   </si>
   <si>
     <t>Red</t>
